--- a/Result/checksun_type/控制器.xlsx
+++ b/Result/checksun_type/控制器.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>630.2</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>694.75</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>770.74</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>694.75</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>770.74</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>95711.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>184090.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>184090</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>238520.8</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>625496.02</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>625496.02</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-59407.18447863078</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>95711</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>95711.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>630.2</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>701.25</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>771.56</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>701.25</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>771.5599999999999</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>181105.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>213249.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>213249.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>261286.0</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>631907.8</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>631907.8</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-54134.00295314955</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>181105</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>181105.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>631.4</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>706.0</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>772.34</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>706</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>772.34</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>135802.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>252624.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>252624</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>286992.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>639483.2</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>639483.2</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-53816.8863827067</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>135802</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>135802.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>641.0</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>712.35</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>773.42</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>712.35</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>773.42</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>262274.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>287562.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>287562.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>323456.1</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>664782.5</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>664782.5</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-46587.93819697743</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>262274</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>262274.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>657.8</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>718.95</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>774.36</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>718.95</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>774.36</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>245558.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>296429.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>296429.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>325427.2</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>674644.66</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>674644.66</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-48147.58585318638</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>245558</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>245558.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>671.6</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>725.65</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>773.56</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>725.65</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>773.5599999999999</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>241508.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>292951.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>292951.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>382000.7</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>675976.12</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>675976.12</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-46865.09729587106</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>241508</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>241508.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>686.2</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>733.3</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>772.84</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>733.3</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>772.84</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>377978.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>309322.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>309322.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>400021.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>677723.46</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>677723.46</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-42925.28873913951</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>377978</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>377978.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>702.8</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>740.6</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>771.72</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>740.6</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>771.72</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>310495.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>321361.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>321361.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>392151.7</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>673300.18</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>673300.1800000001</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-50385.73048883944</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>310495</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>310495.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>711.8</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>747.5</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>770.14</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>747.5</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>770.14</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>306608.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>359349.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>359349.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>389319.8</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>672018.02</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>672018.02</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-52013.69261380937</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>306608</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>306608.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>722.4</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>754.55</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>768.06</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>754.55</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>768.0599999999999</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>228169.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>354425.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>354425</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>390521.3</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>675976.46</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>675976.46</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-52065.25662755885</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>228169</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>228169.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>735.0</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>760.7</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>766.1</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>760.7</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>766.1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>323363.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>471049.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>471049.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>445989.1</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>679269.88</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>679269.88</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-41875.26748193102</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>323363</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>323363.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>19.45</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>20.26</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>21.48</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>21.48</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>446.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>537.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>537.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>724.2</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>1332.24</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>1332.24</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-141.0385748025855</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>446</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>446.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>19.31</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>20.36</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>21.54</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>20.36</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>21.54</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>166.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>494.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>494.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>754.3</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>1394.4</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>1394.4</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-143.6359791514134</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>166</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>19.25</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>20.49</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>21.61</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>21.61</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>290.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>804.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>804</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>822.2</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>1439.06</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>1439.06</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-112.2167003943315</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>290</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>290.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>19.42</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>20.64</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>21.68</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>21.68</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>1287.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>930.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>930.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>895.9</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>1833.62</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>1833.62</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-76.60999144155971</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>1287</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>1287.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>19.67</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>20.79</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>21.75</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>21.75</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>497.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>738.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>738.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>769.3</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>1851.22</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>1851.22</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-129.8286218146873</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>497</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>497.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>19.86</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>20.94</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>21.81</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>21.81</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>231.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>911.2</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>911.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>794.5</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>1867.82</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>1867.82</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-116.5756429972018</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>231</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>231.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>20.17</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>21.1</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>21.86</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>21.86</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>1715.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>1014.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>1014.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>834.8</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>1896.36</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>1896.36</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-64.97940029375127</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>1715</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>1715.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>20.44</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>21.27</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>21.92</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>21.27</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>21.92</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>922.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>840.4</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>840.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>714.3</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>1889.2</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>1889.2</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-147.9497892783307</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>922</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>922.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>20.46</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>21.43</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>21.96</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>21.96</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>326.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>861.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>861.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>702.8</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>2075.44</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>2075.44</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-176.2307096392179</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>326</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>326.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>20.53</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>21.46</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>22.01</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>21.46</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>22.01</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>1362.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>800.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>800.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>791.6</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>2169.22</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>2169.22</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-146.4809276676563</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>1362</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>1362.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>20.6</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>21.49</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>22.08</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>22.08</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>747.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>677.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>677.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>999.4</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>2614.76</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>2614.76</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-209.7497774344375</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>747</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>747.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>210.0</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>201.08</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>194.92</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>201.08</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>194.92</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>27093.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>25064.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>25064</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>22168.4</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>12662.48</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>12662.48</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>2440.878634307883</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>27093</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>27093.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>207.4</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>200.3</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>194.34</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>200.3</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>194.34</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>27123.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>21655.6</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>21655.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>20056.7</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>12284.3</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>12284.3</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>2293.457328001074</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>27123</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>27123.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>204.5</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>199.48</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>193.8</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>199.48</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>193.8</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>22122.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>20551.2</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>20551.2</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>18187.0</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>11819.44</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>11819.44</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>1997.731985848452</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>22122</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>22122.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>203.2</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>198.92</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>193.33</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>198.92</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>193.33</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>26279.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>21604.4</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>21604.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>18148.2</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>11512.0</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>11512</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>2039.741068992971</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>26279</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>26279.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>202.1</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>198.58</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>192.93</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>198.58</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>192.93</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>22703.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>23070.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>23070.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>16467.7</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>11056.48</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>11056.48</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>1581.513292449679</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>22703</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>22703.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>200.6</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>198.25</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>192.58</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>198.25</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>192.58</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>10051.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>19272.8</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>19272.8</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>14943.0</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>10672.76</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>10672.76</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>1253.562422657489</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>10051</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>10051.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>200.0</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>197.98</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>192.28</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>197.98</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>192.28</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>21601.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>18457.8</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>18457.8</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>15697.4</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>10622.98</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>10622.98</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>2095.862522145168</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>21601</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>21601.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>199.5</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>197.7</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>192.01</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>197.7</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>192.01</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>27388.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>15822.8</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>15822.8</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>14450.7</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>10277.46</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>10277.46</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>1986.79614562238</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>27388</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>27388.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>198.8</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>197.15</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>191.65</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>197.15</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>191.65</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>33609.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>14692.0</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>14692</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>12138.8</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>9836.78</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>9836.780000000001</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>1139.994316817598</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>33609</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>33609.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>197.9</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>196.78</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>191.34</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>196.78</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>191.34</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>3715.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>9865.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>9865</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>9864.3</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>9269.96</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>9269.959999999999</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-776.9723785041442</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>3715</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>3715.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>198.2</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>196.62</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>191.17</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>196.62</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>191.17</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>5976.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>10613.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>10613.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>10254.6</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>9315.64</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>9315.639999999999</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-284.8186440172012</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>5976</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>5976.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>

--- a/Result/checksun_type/控制器.xlsx
+++ b/Result/checksun_type/控制器.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【d1】;【d2】</t>
+          <t>價_量;【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1188.0</t>
+          <t>382.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>60.48</t>
+          <t>62.72</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-14.71</t>
+          <t>-15.65</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>75.65</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>91.88</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>3.75</v>
+        <v>0.59</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.88</v>
+        <v>5.95</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-11.73</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>698.8</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>672.7</v>
+        <v>672.75</v>
       </c>
       <c r="AN2" t="n">
-        <v>765</v>
+        <v>762.16</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>706.65</t>
+          <t>709.39</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>59.04</t>
+          <t>67.78</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-9.970000000000001</v>
+        <v>-6.7</v>
       </c>
       <c r="AR2" t="n">
-        <v>-24.33</v>
+        <v>-20.8</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-127.05</t>
+          <t>-123.13</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>415826.0423452768</t>
+          <t>415803.5113636364</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>903157.0</t>
+          <t>272591.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>595512.6</v>
+        <v>626091.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>371093.3</t>
+          <t>384772.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>588379.48</v>
+        <v>572103.12</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>224419</t>
+          <t>241319</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-11817.63491464496</t>
+          <t>-1081.15954377422</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>89642.95156067307</t>
+          <t>57969.45499601483</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>903157.0</t>
+          <t>272591.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>177.25</t>
+          <t>174.19</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>19.10</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>61.34</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>764.0</t>
+          <t>708.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>790.0</t>
+          <t>724.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>705.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1760.0</t>
+          <t>1188.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>753.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>45.66</t>
+          <t>60.48</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-14.71</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>54.98</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>75.65</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>97.78</t>
+          <t>91.88</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>9.960000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.63</v>
+        <v>3.88</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-12.05</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>684.8</t>
+          <t>698.8</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>673.8</v>
+        <v>672.7</v>
       </c>
       <c r="AN3" t="n">
-        <v>766.12</v>
+        <v>765</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>703.69</t>
+          <t>706.65</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>59.04</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-14.8</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>-27.92</v>
+        <v>-24.33</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-131.04</t>
+          <t>-127.05</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>415826.0423452768</t>
+          <t>415803.5113636364</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1328842.0</t>
+          <t>903157.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>447171.2</v>
+        <v>595512.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>307005.0</t>
+          <t>371093.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>581707.48</v>
+        <v>588379.48</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>140166</t>
+          <t>224419</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-30265.01427379369</t>
+          <t>-11817.63491464496</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>64128.62695444649</t>
+          <t>89642.95156067307</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1328842.0</t>
+          <t>903157.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>187.95</t>
+          <t>177.25</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>19.84</t>
+          <t>19.10</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>61.34</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>733.0</t>
+          <t>764.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>783.0</t>
+          <t>790.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>753.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1715,7 +1715,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>6739</t>
@@ -1723,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>696.0</t>
+          <t>1760.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1738,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>753.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1748,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>45.66</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1823,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-15.65</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1833,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>54.98</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1854,12 +1858,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1869,51 +1873,51 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>91.85</t>
+          <t>97.78</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>8.34</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1.9</v>
+        <v>1.63</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>-12.05</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>661.8</t>
+          <t>684.8</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>674.65</v>
+        <v>673.8</v>
       </c>
       <c r="AN4" t="n">
-        <v>766.6799999999999</v>
+        <v>766.12</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>700.39</t>
+          <t>703.69</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-23.61</v>
+        <v>-14.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>-31.2</v>
+        <v>-27.92</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1922,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-134.68</t>
+          <t>-131.04</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1932,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>415826.0423452768</t>
+          <t>415803.5113636364</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>485201.0</t>
+          <t>1328842.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>213263.2</v>
+        <v>447171.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>198676.6</t>
+          <t>307005.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>573003.24</v>
+        <v>581707.48</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>14586</t>
+          <t>140166</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-47427.49449711009</t>
+          <t>-30265.01427379369</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-20219.82344567886</t>
+          <t>64128.62695444649</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>485201.0</t>
+          <t>1328842.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1988,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>174.19</t>
+          <t>187.95</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2033,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2043,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>19.84</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2058,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>61.34</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2073,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2098,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>658.0</t>
+          <t>733.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>783.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>753.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2133,7 +2137,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>6739</t>
@@ -2141,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>696.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2156,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2166,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2241,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-23.29</t>
+          <t>-15.65</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2251,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2272,17 +2280,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2291,47 +2299,47 @@
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.87</v>
+        <v>8.34</v>
       </c>
       <c r="AI5" t="n">
-        <v>-4.26</v>
+        <v>-1.9</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.96</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>646.4</t>
+          <t>661.8</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>675.15</v>
+        <v>674.65</v>
       </c>
       <c r="AN5" t="n">
-        <v>766.86</v>
+        <v>766.6799999999999</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>697.59</t>
+          <t>700.39</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-30.84</v>
+        <v>-23.61</v>
       </c>
       <c r="AR5" t="n">
-        <v>-33.1</v>
+        <v>-31.2</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2340,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-136.79</t>
+          <t>-134.68</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2350,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>415826.0423452768</t>
+          <t>415803.5113636364</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>140667.0</t>
+          <t>485201.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>135365.2</v>
+        <v>213263.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>174307.3</t>
+          <t>198676.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>574226.34</v>
+        <v>573003.24</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-38942</t>
+          <t>14586</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-52374.34377918849</t>
+          <t>-47427.49449711009</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-49605.36603708362</t>
+          <t>-20219.82344567886</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>140667.0</t>
+          <t>485201.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2406,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>149.33</t>
+          <t>174.19</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2451,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2476,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>61.34</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2491,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2516,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>669.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>644.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2551,7 +2559,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>6739</t>
@@ -2559,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2574,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2584,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-27.56</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2659,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-23.88</t>
+          <t>-23.29</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2669,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2690,266 +2702,266 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>82.22</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>76.04</t>
+          <t>91.85</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.47</v>
+        <v>0.87</v>
       </c>
       <c r="AI6" t="n">
-        <v>-5.06</v>
+        <v>-4.26</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>-11.96</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
+          <t>646.4</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>675.15</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>766.86</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>697.59</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>6.83</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-30.84</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-33.1</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>89.95</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-136.79</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>415803.5113636364</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>140667.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>135365.2</v>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>174307.3</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>574226.34</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-38942</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-52374.34377918849</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-49605.36603708362</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>140667.0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>261.5</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/05/15</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>149.33</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>5.417317991953463</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>102.0481335952849</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>95.34284575725091</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>17.18</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>9.59</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>60.66</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>66.48%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>53.80%</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>46.32</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>16678</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>竹陞科技-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>647.0</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>669.0</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>644.0</t>
         </is>
       </c>
-      <c r="AM6" t="n">
-        <v>678.35</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>767.8200000000001</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>695.44</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="AQ6" t="n">
-        <v>-33</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>-33.66</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>89.95</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-137.42</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>415826.0423452768</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>119696.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="n">
-        <v>143452.8</v>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>198038.4</t>
-        </is>
-      </c>
-      <c r="AZ6" t="n">
-        <v>598609.88</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>-54585</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-52877.79427775302</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>-52898.73523776597</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>119696.0</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>261.5</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/05/15</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>147.42</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>5.417317991953463</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>102.0481335952849</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>95.34284575725091</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>17.04</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>9.59</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>61.34</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>66.48%</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>53.80%</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>46.08</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>16864</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>竹陞科技-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>663.0</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>663.0</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>637.0</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2971,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2981,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>249.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2996,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3006,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-32.45</t>
+          <t>-27.56</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3081,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-22.94</t>
+          <t>-23.88</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3091,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3112,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>60.54</t>
+          <t>76.04</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>2.47</v>
+        <v>0.47</v>
       </c>
       <c r="AI7" t="n">
-        <v>-6.43</v>
+        <v>-5.06</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.22</t>
+          <t>-11.65</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>639.2</t>
+          <t>644.0</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>683.15</v>
+        <v>678.35</v>
       </c>
       <c r="AN7" t="n">
-        <v>769.46</v>
+        <v>767.8200000000001</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>692.9</t>
+          <t>695.44</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-34.77</v>
+        <v>-33</v>
       </c>
       <c r="AR7" t="n">
-        <v>-33.83</v>
+        <v>-33.66</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3180,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-137.60</t>
+          <t>-137.42</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3190,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>415826.0423452768</t>
+          <t>415803.5113636364</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>146674</v>
+        <v>143452.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>217118.3</t>
+          <t>198038.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>615716.62</v>
+        <v>598609.88</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-70444</t>
+          <t>-54585</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-52873.98683047794</t>
+          <t>-52877.79427775302</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-53467.41498024913</t>
+          <t>-52898.73523776597</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3246,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>150.48</t>
+          <t>147.42</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3291,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3301,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3316,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>61.34</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3331,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3356,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>656.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3403,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>247.0</t>
+          <t>249.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3418,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3428,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-27.97</t>
+          <t>-32.45</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3503,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-22.94</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3513,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3534,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>60.54</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>1.24</v>
+        <v>2.47</v>
       </c>
       <c r="AI8" t="n">
-        <v>-8.51</v>
+        <v>-6.43</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-10.5</t>
+          <t>-11.22</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>630.2</t>
+          <t>639.2</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>688.8</v>
+        <v>683.15</v>
       </c>
       <c r="AN8" t="n">
-        <v>769.62</v>
+        <v>769.46</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>690.04</t>
+          <t>692.9</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-11.17</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-37.34</v>
+        <v>-34.77</v>
       </c>
       <c r="AR8" t="n">
-        <v>-33.59</v>
+        <v>-33.83</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3602,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-137.34</t>
+          <t>-137.60</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3612,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>415826.0423452768</t>
+          <t>415803.5113636364</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>159302.0</t>
+          <t>161450.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>166838.8</v>
+        <v>146674</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>231634.1</t>
+          <t>217118.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>622148.62</v>
+        <v>615716.62</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-64795</t>
+          <t>-70444</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-52766.09080324681</t>
+          <t>-52873.98683047794</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-56843.90693450192</t>
+          <t>-53467.41498024913</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>159302.0</t>
+          <t>161450.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3668,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>150.48</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3713,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3723,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3738,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>61.34</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3753,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3778,12 +3790,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>651.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>658.0</t>
+          <t>656.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3793,7 +3805,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3825,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3840,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3850,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>11.72</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-22.82</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3925,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3935,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3956,38 +3968,38 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="AI9" t="n">
-        <v>-9.289999999999999</v>
+        <v>-8.51</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-9.86</t>
+          <t>-10.5</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -3996,26 +4008,26 @@
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>694.75</v>
+        <v>688.8</v>
       </c>
       <c r="AN9" t="n">
-        <v>770.74</v>
+        <v>769.62</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>687.31</t>
+          <t>690.04</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-17.45</t>
+          <t>-11.17</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-38.35</v>
+        <v>-37.34</v>
       </c>
       <c r="AR9" t="n">
-        <v>-32.65</v>
+        <v>-33.59</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4024,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-136.30</t>
+          <t>-137.34</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4034,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>415826.0423452768</t>
+          <t>415803.5113636364</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>184090</v>
+        <v>166838.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>238520.8</t>
+          <t>231634.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>625496.02</v>
+        <v>622148.62</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-54430</t>
+          <t>-64795</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-52024.66968847315</t>
+          <t>-52766.09080324681</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-59407.18447863078</t>
+          <t>-56843.90693450192</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4090,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4135,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4160,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>61.34</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4175,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4200,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>651.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>636.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4247,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>283.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4272,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>11.72</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-18.38</t>
+          <t>-22.82</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4357,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4378,38 +4390,38 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>30.93</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="AH10" t="n">
         <v>1.56</v>
       </c>
       <c r="AI10" t="n">
-        <v>-10.13</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-9.11</t>
+          <t>-9.86</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -4418,26 +4430,26 @@
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>701.25</v>
+        <v>694.75</v>
       </c>
       <c r="AN10" t="n">
-        <v>771.5599999999999</v>
+        <v>770.74</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>684.56</t>
+          <t>687.31</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-25.78</t>
+          <t>-17.45</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-39.28</v>
+        <v>-38.35</v>
       </c>
       <c r="AR10" t="n">
-        <v>-31.23</v>
+        <v>-32.65</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4446,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-134.72</t>
+          <t>-136.30</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4456,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>415826.0423452768</t>
+          <t>415803.5113636364</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>213249.4</v>
+        <v>184090</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>261286.0</t>
+          <t>238520.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>631907.8</v>
+        <v>625496.02</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-48036</t>
+          <t>-54430</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-50682.39427208085</t>
+          <t>-52024.66968847315</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-54134.00295314955</t>
+          <t>-59407.18447863078</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4557,12 +4569,12 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4572,7 +4584,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4582,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>61.34</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4597,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4622,17 +4634,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>629.0</t>
+          <t>636.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4669,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>283.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4684,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4694,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-18.38</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4769,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-26.71</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4779,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4800,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AI11" t="n">
-        <v>-10.57</v>
+        <v>-10.13</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-9.11</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>631.4</t>
+          <t>630.2</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>706</v>
+        <v>701.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>772.34</v>
+        <v>771.5599999999999</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>681.75</t>
+          <t>684.56</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-36.56</t>
+          <t>-25.78</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-39.9</v>
+        <v>-39.28</v>
       </c>
       <c r="AR11" t="n">
-        <v>-29.22</v>
+        <v>-31.23</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4868,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-132.48</t>
+          <t>-134.72</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4878,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>415826.0423452768</t>
+          <t>415803.5113636364</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>252624</v>
+        <v>213249.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>286992.7</t>
+          <t>261286.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>639483.2</v>
+        <v>631907.8</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-34368</t>
+          <t>-48036</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-50054.82905734108</t>
+          <t>-50682.39427208085</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-53816.8863827067</t>
+          <t>-54134.00295314955</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4934,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>138.24</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4979,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -4989,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>16.41</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5004,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>61.34</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5019,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5044,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>654.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>629.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5091,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5106,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5116,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-11.10</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5191,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-28.24</t>
+          <t>-26.71</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5201,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5222,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-4.84</v>
+        <v>-1.33</v>
       </c>
       <c r="AI12" t="n">
-        <v>-10.02</v>
+        <v>-10.57</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-7.9</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>641.0</t>
+          <t>631.4</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>712.35</v>
+        <v>706</v>
       </c>
       <c r="AN12" t="n">
-        <v>773.42</v>
+        <v>772.34</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>679.24</t>
+          <t>681.75</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-44.55</t>
+          <t>-36.56</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-38.37</v>
+        <v>-39.9</v>
       </c>
       <c r="AR12" t="n">
-        <v>-26.55</v>
+        <v>-29.22</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5290,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-129.51</t>
+          <t>-132.48</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5300,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>415826.0423452768</t>
+          <t>415803.5113636364</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>287562.6</v>
+        <v>252624</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>323456.1</t>
+          <t>286992.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>664782.5</v>
+        <v>639483.2</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-35893</t>
+          <t>-34368</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-49370.81863454734</t>
+          <t>-50054.82905734108</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-46587.93819697743</t>
+          <t>-53816.8863827067</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5356,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>133.27</t>
+          <t>138.24</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5401,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5411,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.41</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5426,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>61.34</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5441,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5466,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>624.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>630.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>600.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5503,7 +5515,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5513,12 +5525,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5548,7 +5560,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5623,17 +5635,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5649,61 +5661,61 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>68.18</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>75.67</t>
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>-0.44</v>
+        <v>-0.39</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>20.34</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>19.96</v>
+        <v>19.97</v>
       </c>
       <c r="AN13" t="n">
-        <v>21.24</v>
+        <v>21.17</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>21.99</t>
+          <t>21.94</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AQ13" t="n">
-        <v>-0.25</v>
+        <v>-0.22</v>
       </c>
       <c r="AR13" t="n">
-        <v>-0.42</v>
+        <v>-0.38</v>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
@@ -5712,7 +5724,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-106.36</t>
+          <t>-105.75</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5722,43 +5734,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>30081.33144475921</t>
+          <t>30039.46888260255</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>323.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>410.4</v>
+        <v>408.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>379.6</t>
+          <t>382.9</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>1080.7</v>
+        <v>1030.88</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-119.2499695063228</t>
+          <t>-115.6021222454177</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-99.02285334736263</t>
+          <t>-95.5389623104395</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>323.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5823,7 +5835,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5863,7 +5875,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -5888,17 +5900,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -5925,7 +5937,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5935,12 +5947,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5950,7 +5962,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5960,7 +5972,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -5970,7 +5982,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-6.97</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6035,7 +6047,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-7.32</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6045,17 +6057,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6071,61 +6083,61 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>98.48</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>1.63</v>
+        <v>-0.44</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.39</v>
+        <v>1.88</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-6.16</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.34</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>19.99</v>
+        <v>19.96</v>
       </c>
       <c r="AN14" t="n">
-        <v>21.3</v>
+        <v>21.24</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="AQ14" t="n">
-        <v>-0.28</v>
+        <v>-0.25</v>
       </c>
       <c r="AR14" t="n">
-        <v>-0.46</v>
+        <v>-0.42</v>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
@@ -6134,7 +6146,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-107.02</t>
+          <t>-106.36</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6144,43 +6156,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>30081.33144475921</t>
+          <t>30039.46888260255</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>431.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>449.8</v>
+        <v>410.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>483.5</t>
+          <t>379.6</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>1229.92</v>
+        <v>1080.7</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-33</t>
+          <t>30</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-122.9276269897701</t>
+          <t>-119.2499695063228</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-92.42759578056138</t>
+          <t>-99.02285334736263</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>431.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6200,7 +6212,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-12.90</t>
+          <t>-14.38</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6245,7 +6257,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6255,7 +6267,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6285,7 +6297,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6310,22 +6322,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="CG14" t="inlineStr">
+        <is>
           <t>20.25</t>
-        </is>
-      </c>
-      <c r="CG14" t="inlineStr">
-        <is>
-          <t>20.6</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6347,7 +6359,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6357,12 +6369,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6372,7 +6384,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6382,7 +6394,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6392,7 +6404,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-6.97</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6457,7 +6469,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6467,17 +6479,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6493,7 +6505,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6507,47 +6519,47 @@
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>1</v>
+        <v>1.63</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.49</v>
+        <v>1.39</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.16</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>20</v>
+        <v>19.99</v>
       </c>
       <c r="AN15" t="n">
-        <v>21.33</v>
+        <v>21.3</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>30.88</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="AQ15" t="n">
-        <v>-0.35</v>
+        <v>-0.28</v>
       </c>
       <c r="AR15" t="n">
-        <v>-0.51</v>
+        <v>-0.46</v>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
@@ -6556,7 +6568,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-107.72</t>
+          <t>-107.02</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6566,43 +6578,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>30081.33144475921</t>
+          <t>30039.46888260255</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>444.0</t>
+          <t>431.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>443</v>
+        <v>449.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>490.1</t>
+          <t>483.5</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>1239.7</v>
+        <v>1229.92</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-47</t>
+          <t>-33</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-128.4730872096262</t>
+          <t>-122.9276269897701</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-99.31195655011089</t>
+          <t>-92.42759578056138</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>444.0</t>
+          <t>431.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6622,7 +6634,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>-12.90</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6667,7 +6679,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6677,7 +6689,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6707,7 +6719,7 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6732,22 +6744,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6769,7 +6781,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6779,12 +6791,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6794,7 +6806,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6804,17 +6816,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-9.61</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6879,7 +6891,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-7.32</t>
+          <t>-7.09</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -6889,17 +6901,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -6915,12 +6927,12 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>95.45</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -6929,47 +6941,47 @@
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.08</v>
+        <v>0.49</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AM16" t="n">
         <v>20</v>
       </c>
       <c r="AN16" t="n">
-        <v>21.36</v>
+        <v>21.33</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>25.28</t>
+          <t>30.88</t>
         </is>
       </c>
       <c r="AQ16" t="n">
-        <v>-0.41</v>
+        <v>-0.35</v>
       </c>
       <c r="AR16" t="n">
-        <v>-0.55</v>
+        <v>-0.51</v>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
@@ -6978,7 +6990,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-108.32</t>
+          <t>-107.72</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -6988,43 +7000,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>30081.33144475921</t>
+          <t>30039.46888260255</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>597.0</t>
+          <t>444.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>443.4</v>
+        <v>443</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>468.8</t>
+          <t>490.1</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>1250.78</v>
+        <v>1239.7</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-25</t>
+          <t>-47</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-133.7751109659018</t>
+          <t>-128.4730872096262</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-106.9927592012491</t>
+          <t>-99.31195655011089</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>597.0</t>
+          <t>444.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7044,7 +7056,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-14.38</t>
+          <t>-14.16</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7089,7 +7101,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7129,7 +7141,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7154,22 +7166,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7189,7 +7201,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>3623</t>
@@ -7197,12 +7213,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7212,7 +7228,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7222,7 +7238,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7232,7 +7248,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7297,7 +7313,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-7.32</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7307,17 +7323,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7333,61 +7349,61 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.45</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>98.48</t>
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>2.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI17" t="n">
-        <v>-0.79</v>
+        <v>0.08</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-6.4</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>20.02</v>
+        <v>20</v>
       </c>
       <c r="AN17" t="n">
-        <v>21.39</v>
+        <v>21.36</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>25.28</t>
         </is>
       </c>
       <c r="AQ17" t="n">
-        <v>-0.47</v>
+        <v>-0.41</v>
       </c>
       <c r="AR17" t="n">
-        <v>-0.58</v>
+        <v>-0.55</v>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
@@ -7396,7 +7412,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-108.84</t>
+          <t>-108.32</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7406,43 +7422,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>30081.33144475921</t>
+          <t>30039.46888260255</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>332.0</t>
+          <t>597.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>357.2</v>
+        <v>443.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>580.6</t>
+          <t>468.8</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>1257.56</v>
+        <v>1250.78</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-223</t>
+          <t>-25</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-138.6446294685659</t>
+          <t>-133.7751109659018</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-130.5370215885447</t>
+          <t>-106.9927592012491</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>332.0</t>
+          <t>597.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7462,7 +7478,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>-14.38</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7507,7 +7523,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7547,7 +7563,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7572,22 +7588,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7607,7 +7623,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>3623</t>
@@ -7615,12 +7635,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7630,7 +7650,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7640,7 +7660,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7650,7 +7670,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-45.47</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7715,7 +7735,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-8.92</t>
+          <t>-7.09</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7725,17 +7745,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7751,7 +7771,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7761,51 +7781,51 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>1.32</v>
+        <v>2.22</v>
       </c>
       <c r="AI18" t="n">
-        <v>-2.17</v>
+        <v>-0.79</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.4</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>19.64</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>20.08</v>
+        <v>20.02</v>
       </c>
       <c r="AN18" t="n">
-        <v>21.41</v>
+        <v>21.39</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.21</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>18.96</t>
         </is>
       </c>
       <c r="AQ18" t="n">
-        <v>-0.55</v>
+        <v>-0.47</v>
       </c>
       <c r="AR18" t="n">
-        <v>-0.61</v>
+        <v>-0.58</v>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
@@ -7814,7 +7834,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-109.26</t>
+          <t>-108.84</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7824,43 +7844,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>30081.33144475921</t>
+          <t>30039.46888260255</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>445.0</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>348.8</v>
+        <v>357.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>639.6</t>
+          <t>580.6</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>1276.44</v>
+        <v>1257.56</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-290</t>
+          <t>-223</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-140.1187399922061</t>
+          <t>-138.6446294685659</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-131.1167885136618</t>
+          <t>-130.5370215885447</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>445.0</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -7880,7 +7900,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-15.86</t>
+          <t>-14.16</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -7925,7 +7945,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -7935,7 +7955,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -7965,7 +7985,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -7995,7 +8015,7 @@
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
@@ -8005,7 +8025,7 @@
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8025,7 +8045,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>3623</t>
@@ -8033,12 +8057,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8048,7 +8072,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8058,7 +8082,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8068,7 +8092,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-17.60</t>
+          <t>-45.47</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8133,7 +8157,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-8.92</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8143,17 +8167,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8169,61 +8193,61 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AI19" t="n">
-        <v>-3.26</v>
+        <v>-2.17</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.64</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>20.16</v>
+        <v>20.08</v>
       </c>
       <c r="AN19" t="n">
-        <v>21.44</v>
+        <v>21.41</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AQ19" t="n">
-        <v>-0.6</v>
+        <v>-0.55</v>
       </c>
       <c r="AR19" t="n">
-        <v>-0.63</v>
+        <v>-0.61</v>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
@@ -8232,7 +8256,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-109.49</t>
+          <t>-109.26</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8242,43 +8266,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>30081.33144475921</t>
+          <t>30039.46888260255</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>397.0</t>
+          <t>445.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>517.2</v>
+        <v>348.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>627.7</t>
+          <t>639.6</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>1309.6</v>
+        <v>1276.44</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-290</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-141.7554584428505</t>
+          <t>-140.1187399922061</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-139.3694273883414</t>
+          <t>-131.1167885136618</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>397.0</t>
+          <t>445.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8298,7 +8322,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-16.49</t>
+          <t>-15.86</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8343,7 +8367,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8353,7 +8377,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8383,7 +8407,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8408,22 +8432,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8445,7 +8469,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8455,12 +8479,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8470,7 +8494,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8480,7 +8504,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8490,7 +8514,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-25.82</t>
+          <t>-17.60</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8555,7 +8579,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-9.15</t>
+          <t>-9.61</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8565,17 +8589,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8591,28 +8615,28 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>2.06</v>
+        <v>1.28</v>
       </c>
       <c r="AI20" t="n">
-        <v>-4.02</v>
+        <v>-3.26</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -8622,27 +8646,27 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>20.26</v>
+        <v>20.16</v>
       </c>
       <c r="AN20" t="n">
-        <v>21.48</v>
+        <v>21.44</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AQ20" t="n">
-        <v>-0.64</v>
+        <v>-0.6</v>
       </c>
       <c r="AR20" t="n">
         <v>-0.63</v>
@@ -8654,7 +8678,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-109.58</t>
+          <t>-109.49</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8664,43 +8688,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>30081.33144475921</t>
+          <t>30039.46888260255</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>446.0</t>
+          <t>397.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>537.2</v>
+        <v>517.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>724.2</t>
+          <t>627.7</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>1332.24</v>
+        <v>1309.6</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-187</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-142.1892822709431</t>
+          <t>-141.7554584428505</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-141.0385748025855</t>
+          <t>-139.3694273883414</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>446.0</t>
+          <t>397.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8720,7 +8744,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-16.07</t>
+          <t>-16.49</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8765,17 +8789,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8805,7 +8829,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -8830,22 +8854,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -8877,12 +8901,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -8892,7 +8916,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8902,7 +8926,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -8912,7 +8936,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-34.48</t>
+          <t>-25.82</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -8977,7 +9001,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-10.76</t>
+          <t>-9.15</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -8987,17 +9011,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9013,58 +9037,58 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>0.98</v>
+        <v>2.06</v>
       </c>
       <c r="AI21" t="n">
-        <v>-5.18</v>
+        <v>-4.02</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-5.44</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>20.36</v>
+        <v>20.26</v>
       </c>
       <c r="AN21" t="n">
-        <v>21.54</v>
+        <v>21.48</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-10.91</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AQ21" t="n">
-        <v>-0.7</v>
+        <v>-0.64</v>
       </c>
       <c r="AR21" t="n">
         <v>-0.63</v>
@@ -9076,7 +9100,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-109.53</t>
+          <t>-109.58</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9086,43 +9110,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>30081.33144475921</t>
+          <t>30039.46888260255</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>446.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>494.2</v>
+        <v>537.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>754.3</t>
+          <t>724.2</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>1394.4</v>
+        <v>1332.24</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-260</t>
+          <t>-187</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-142.3985018106445</t>
+          <t>-142.1892822709431</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-143.6359791514134</t>
+          <t>-141.0385748025855</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>446.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9142,7 +9166,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-17.55</t>
+          <t>-16.07</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9187,17 +9211,17 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9227,7 +9251,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9252,22 +9276,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9299,42 +9323,42 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>5.19</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9399,7 +9423,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-12.13</t>
+          <t>-10.76</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9409,17 +9433,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9435,45 +9459,45 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>26.92</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>-0.26</v>
+        <v>0.98</v>
       </c>
       <c r="AI22" t="n">
-        <v>-6.04</v>
+        <v>-5.18</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>20.49</v>
+        <v>20.36</v>
       </c>
       <c r="AN22" t="n">
-        <v>21.61</v>
+        <v>21.54</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9482,14 +9506,14 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-17.72</t>
+          <t>-10.91</t>
         </is>
       </c>
       <c r="AQ22" t="n">
-        <v>-0.72</v>
+        <v>-0.7</v>
       </c>
       <c r="AR22" t="n">
-        <v>-0.61</v>
+        <v>-0.63</v>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
@@ -9498,7 +9522,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-109.53</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9508,43 +9532,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>30081.33144475921</t>
+          <t>30039.46888260255</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>290.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>804</v>
+        <v>494.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>822.2</t>
+          <t>754.3</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>1439.06</v>
+        <v>1394.4</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-260</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-142.1735059305047</t>
+          <t>-142.3985018106445</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-112.2167003943315</t>
+          <t>-143.6359791514134</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>290.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9564,7 +9588,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-18.82</t>
+          <t>-17.55</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9609,7 +9633,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9619,7 +9643,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9649,7 +9673,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9674,22 +9698,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
           <t>19.3</t>
         </is>
       </c>
-      <c r="CF22" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9721,12 +9745,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9756,7 +9780,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9831,17 +9855,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -9857,7 +9881,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -9867,51 +9891,51 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>-1.13</v>
+        <v>-0.26</v>
       </c>
       <c r="AI23" t="n">
-        <v>-5.9</v>
+        <v>-6.04</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>19.42</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>20.64</v>
+        <v>20.49</v>
       </c>
       <c r="AN23" t="n">
-        <v>21.68</v>
+        <v>21.61</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>22.37</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-21.10</t>
+          <t>-17.72</t>
         </is>
       </c>
       <c r="AQ23" t="n">
-        <v>-0.71</v>
+        <v>-0.72</v>
       </c>
       <c r="AR23" t="n">
-        <v>-0.58</v>
+        <v>-0.61</v>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
@@ -9920,7 +9944,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-108.86</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -9930,43 +9954,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>30081.33144475921</t>
+          <t>30039.46888260255</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1287.0</t>
+          <t>290.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>930.4</v>
+        <v>804</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>895.9</t>
+          <t>822.2</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>1833.62</v>
+        <v>1439.06</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-147.6201978461726</t>
+          <t>-142.1735059305047</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-76.60999144155971</t>
+          <t>-112.2167003943315</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>1287.0</t>
+          <t>290.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10031,7 +10055,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10071,7 +10095,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10096,17 +10120,17 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
@@ -10143,12 +10167,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10158,72 +10182,72 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>-36.13</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2025-12-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>201.5</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
           <t>208.5</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>-40.81</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>2025-12-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>208.5</t>
-        </is>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -10238,12 +10262,12 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -10253,17 +10277,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -10274,66 +10298,66 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>-1.47</v>
+        <v>-0.43</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.31</v>
+        <v>1.74</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>211.6</t>
+          <t>210.9</t>
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>206.82</v>
+        <v>207.3</v>
       </c>
       <c r="AN24" t="n">
-        <v>198.55</v>
+        <v>199.02</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>194.48</t>
+          <t>194.72</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-10.79</t>
         </is>
       </c>
       <c r="AQ24" t="n">
-        <v>4.15</v>
+        <v>3.85</v>
       </c>
       <c r="AR24" t="n">
-        <v>4.43</v>
+        <v>4.31</v>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
@@ -10342,7 +10366,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-55.79</t>
+          <t>-56.95</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -10352,48 +10376,48 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>28204.36402266289</t>
+          <t>28191.54526166902</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>8991.0</t>
+          <t>12761.0</t>
         </is>
       </c>
       <c r="AX24" t="n">
-        <v>9192.6</v>
+        <v>9321.200000000001</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>15530.9</t>
+          <t>14594.8</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>13076.72</v>
+        <v>13234.36</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>-6338</t>
+          <t>-5273</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>107.8641564708477</t>
+          <t>-126.5494017847041</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-1635.124825374487</t>
+          <t>-1415.823972190239</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>8991.0</t>
+          <t>12761.0</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF24" t="inlineStr">
@@ -10408,7 +10432,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -10453,7 +10477,7 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -10463,12 +10487,12 @@
       </c>
       <c r="BS24" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BT24" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU24" t="inlineStr">
@@ -10478,7 +10502,7 @@
       </c>
       <c r="BV24" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="BW24" t="inlineStr">
@@ -10493,12 +10517,12 @@
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>9987</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -10518,22 +10542,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>207.5</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>211.5</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -10555,7 +10579,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -10565,42 +10589,42 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>-1.19</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>43.0</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>208.5</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>24.0</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>211.0</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>-1.2</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-38.92</t>
+          <t>-40.81</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -10660,12 +10684,12 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -10675,17 +10699,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -10696,66 +10720,66 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>47.81</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AH25" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.47</v>
       </c>
       <c r="AI25" t="n">
-        <v>3.27</v>
+        <v>2.31</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>211.6</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>206.25</v>
+        <v>206.82</v>
       </c>
       <c r="AN25" t="n">
-        <v>198.1</v>
+        <v>198.55</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>194.35</t>
+          <t>194.48</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AQ25" t="n">
-        <v>4.63</v>
+        <v>4.15</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.5</v>
+        <v>4.43</v>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
@@ -10764,7 +10788,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>-55.10</t>
+          <t>-55.79</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -10774,43 +10798,43 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>28204.36402266289</t>
+          <t>28191.54526166902</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>5024.0</t>
+          <t>8991.0</t>
         </is>
       </c>
       <c r="AX25" t="n">
-        <v>10541.4</v>
+        <v>9192.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>17259.7</t>
+          <t>15530.9</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>12942.1</v>
+        <v>13076.72</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>-6718</t>
+          <t>-6338</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>424.7712440790905</t>
+          <t>107.8641564708477</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-1486.085871874324</t>
+          <t>-1635.124825374487</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>5024.0</t>
+          <t>8991.0</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -10830,7 +10854,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>9.90</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
@@ -10885,12 +10909,12 @@
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU25" t="inlineStr">
@@ -10900,7 +10924,7 @@
       </c>
       <c r="BV25" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="BW25" t="inlineStr">
@@ -10915,12 +10939,12 @@
       </c>
       <c r="BY25" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>9987</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -10940,22 +10964,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -10987,12 +11011,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11012,7 +11036,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -11022,7 +11046,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-31.72</t>
+          <t>-38.92</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -11097,17 +11121,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12.47</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11118,66 +11142,66 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>73.21</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>-1.26</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AI26" t="n">
-        <v>3.93</v>
+        <v>3.27</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>213.7</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>205.62</v>
+        <v>206.25</v>
       </c>
       <c r="AN26" t="n">
-        <v>197.6</v>
+        <v>198.1</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>194.07</t>
+          <t>194.35</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AQ26" t="n">
-        <v>4.92</v>
+        <v>4.63</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.46</v>
+        <v>4.5</v>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
@@ -11186,7 +11210,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-55.44</t>
+          <t>-55.10</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -11196,43 +11220,43 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>28204.36402266289</t>
+          <t>28191.54526166902</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>11301.0</t>
+          <t>5024.0</t>
         </is>
       </c>
       <c r="AX26" t="n">
-        <v>12991.2</v>
+        <v>10541.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>19027.6</t>
+          <t>17259.7</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>12958.32</v>
+        <v>12942.1</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>-6036</t>
+          <t>-6718</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>772.1998106160748</t>
+          <t>424.7712440790905</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-795.0628714500053</t>
+          <t>-1486.085871874324</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>11301.0</t>
+          <t>5024.0</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -11297,7 +11321,7 @@
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -11312,7 +11336,7 @@
       </c>
       <c r="BT26" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU26" t="inlineStr">
@@ -11322,7 +11346,7 @@
       </c>
       <c r="BV26" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="BW26" t="inlineStr">
@@ -11337,12 +11361,12 @@
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>9987</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -11362,12 +11386,12 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
@@ -11409,12 +11433,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11424,7 +11448,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11434,7 +11458,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -11444,7 +11468,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-14.56</t>
+          <t>-31.72</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -11504,12 +11528,12 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -11519,17 +11543,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>12.47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11540,66 +11564,66 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>86.36</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>90.86</t>
+          <t>73.21</t>
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>-0.14</v>
+        <v>-1.26</v>
       </c>
       <c r="AI27" t="n">
-        <v>4.64</v>
+        <v>3.93</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>214.3</t>
+          <t>213.7</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>204.8</v>
+        <v>205.62</v>
       </c>
       <c r="AN27" t="n">
-        <v>197.13</v>
+        <v>197.6</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>193.75</t>
+          <t>194.07</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>20.18</t>
+          <t>10.33</t>
         </is>
       </c>
       <c r="AQ27" t="n">
-        <v>5.22</v>
+        <v>4.92</v>
       </c>
       <c r="AR27" t="n">
-        <v>4.35</v>
+        <v>4.46</v>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
@@ -11608,7 +11632,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-56.59</t>
+          <t>-55.44</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -11618,43 +11642,43 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>28204.36402266289</t>
+          <t>28191.54526166902</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>8529.0</t>
+          <t>11301.0</t>
         </is>
       </c>
       <c r="AX27" t="n">
-        <v>16149.6</v>
+        <v>12991.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>18902.6</t>
+          <t>19027.6</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>12813</v>
+        <v>12958.32</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>-2752</t>
+          <t>-6036</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>1057.156661900817</t>
+          <t>772.1998106160748</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-452.0277682920532</t>
+          <t>-795.0628714500053</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>8529.0</t>
+          <t>11301.0</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -11674,7 +11698,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>9.90</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -11729,12 +11753,12 @@
       </c>
       <c r="BS27" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BT27" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU27" t="inlineStr">
@@ -11744,7 +11768,7 @@
       </c>
       <c r="BV27" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="BW27" t="inlineStr">
@@ -11759,12 +11783,12 @@
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>9987</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -11784,22 +11808,22 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>212.5</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -11831,12 +11855,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -11846,7 +11870,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>213.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -11856,7 +11880,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -11866,7 +11890,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-14.56</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -11926,12 +11950,12 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -11941,17 +11965,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -11962,38 +11986,38 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>86.21</t>
+          <t>86.36</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>90.86</t>
         </is>
       </c>
       <c r="AH28" t="n">
-        <v>-0.37</v>
+        <v>-0.14</v>
       </c>
       <c r="AI28" t="n">
-        <v>5.15</v>
+        <v>4.64</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
@@ -12002,26 +12026,26 @@
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>203.8</v>
+        <v>204.8</v>
       </c>
       <c r="AN28" t="n">
-        <v>196.6</v>
+        <v>197.13</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>193.37</t>
+          <t>193.75</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>20.18</t>
         </is>
       </c>
       <c r="AQ28" t="n">
-        <v>5.23</v>
+        <v>5.22</v>
       </c>
       <c r="AR28" t="n">
-        <v>4.13</v>
+        <v>4.35</v>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
@@ -12030,7 +12054,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-58.78</t>
+          <t>-56.59</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -12040,43 +12064,43 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>28204.36402266289</t>
+          <t>28191.54526166902</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>12118.0</t>
+          <t>8529.0</t>
         </is>
       </c>
       <c r="AX28" t="n">
-        <v>19868.4</v>
+        <v>16149.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>20209.8</t>
+          <t>18902.6</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>12862.38</v>
+        <v>12813</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>-341</t>
+          <t>-2752</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>1331.553831026793</t>
+          <t>1057.156661900817</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>351.1662279440243</t>
+          <t>-452.0277682920532</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>12118.0</t>
+          <t>8529.0</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -12096,7 +12120,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>11.20</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -12146,7 +12170,7 @@
       </c>
       <c r="BR28" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS28" t="inlineStr">
@@ -12156,7 +12180,7 @@
       </c>
       <c r="BT28" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU28" t="inlineStr">
@@ -12166,7 +12190,7 @@
       </c>
       <c r="BV28" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="BW28" t="inlineStr">
@@ -12181,12 +12205,12 @@
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>9987</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -12211,7 +12235,7 @@
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>217.0</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
@@ -12221,7 +12245,7 @@
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>213.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -12253,12 +12277,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12268,7 +12292,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>213.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -12278,7 +12302,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -12288,7 +12312,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -12348,12 +12372,12 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -12363,17 +12387,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12384,66 +12408,66 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.21</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>0.84</v>
+        <v>-0.37</v>
       </c>
       <c r="AI29" t="n">
-        <v>5.31</v>
+        <v>5.15</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>213.7</t>
+          <t>214.3</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>202.92</v>
+        <v>203.8</v>
       </c>
       <c r="AN29" t="n">
-        <v>196.07</v>
+        <v>196.6</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>193.37</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>35.12</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="AQ29" t="n">
-        <v>5.21</v>
+        <v>5.23</v>
       </c>
       <c r="AR29" t="n">
-        <v>3.85</v>
+        <v>4.13</v>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
@@ -12452,7 +12476,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-61.52</t>
+          <t>-58.78</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -12462,43 +12486,43 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>28204.36402266289</t>
+          <t>28191.54526166902</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>15735.0</t>
+          <t>12118.0</t>
         </is>
       </c>
       <c r="AX29" t="n">
-        <v>21869.2</v>
+        <v>19868.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>21736.8</t>
+          <t>20209.8</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>12717.58</v>
+        <v>12862.38</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>-341</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>1509.806122496388</t>
+          <t>1331.553831026793</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>1101.508857283279</t>
+          <t>351.1662279440243</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>15735.0</t>
+          <t>12118.0</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -12518,7 +12542,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>11.20</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -12563,7 +12587,7 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
@@ -12573,12 +12597,12 @@
       </c>
       <c r="BS29" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT29" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU29" t="inlineStr">
@@ -12588,7 +12612,7 @@
       </c>
       <c r="BV29" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="BW29" t="inlineStr">
@@ -12603,12 +12627,12 @@
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>9987</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -12628,22 +12652,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>217.0</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
         <is>
+          <t>212.5</t>
+        </is>
+      </c>
+      <c r="CG29" t="inlineStr">
+        <is>
           <t>213.5</t>
-        </is>
-      </c>
-      <c r="CG29" t="inlineStr">
-        <is>
-          <t>215.5</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -12675,12 +12699,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -12690,7 +12714,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -12700,7 +12724,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -12710,7 +12734,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -12770,12 +12794,12 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -12785,17 +12809,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -12806,12 +12830,12 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -12825,47 +12849,47 @@
         </is>
       </c>
       <c r="AH30" t="n">
-        <v>1.18</v>
+        <v>0.84</v>
       </c>
       <c r="AI30" t="n">
-        <v>4.99</v>
+        <v>5.31</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>213.7</t>
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>201.92</v>
+        <v>202.92</v>
       </c>
       <c r="AN30" t="n">
-        <v>195.5</v>
+        <v>196.07</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>192.61</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>39.40</t>
+          <t>35.12</t>
         </is>
       </c>
       <c r="AQ30" t="n">
-        <v>4.9</v>
+        <v>5.21</v>
       </c>
       <c r="AR30" t="n">
-        <v>3.51</v>
+        <v>3.85</v>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
@@ -12874,7 +12898,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-64.90</t>
+          <t>-61.52</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -12884,43 +12908,43 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>28204.36402266289</t>
+          <t>28191.54526166902</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>17273.0</t>
+          <t>15735.0</t>
         </is>
       </c>
       <c r="AX30" t="n">
-        <v>23978</v>
+        <v>21869.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>23524.2</t>
+          <t>21736.8</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>12876.32</v>
+        <v>12717.58</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>132</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>1584.041988898771</t>
+          <t>1509.806122496388</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>1746.551582864951</t>
+          <t>1101.508857283279</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>17273.0</t>
+          <t>15735.0</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -12940,7 +12964,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>11.72</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -12985,22 +13009,22 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS30" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT30" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU30" t="inlineStr">
@@ -13010,7 +13034,7 @@
       </c>
       <c r="BV30" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="BW30" t="inlineStr">
@@ -13025,12 +13049,12 @@
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>9987</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -13050,7 +13074,7 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
@@ -13060,12 +13084,12 @@
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>213.5</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -13097,42 +13121,42 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>214.5</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-2.14</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>214.0</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>-2.64</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>13.06</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -13192,12 +13216,12 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -13207,17 +13231,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13228,12 +13252,12 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -13247,47 +13271,47 @@
         </is>
       </c>
       <c r="AH31" t="n">
-        <v>1.9</v>
+        <v>1.18</v>
       </c>
       <c r="AI31" t="n">
-        <v>4.44</v>
+        <v>4.99</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>201.08</v>
+        <v>201.92</v>
       </c>
       <c r="AN31" t="n">
-        <v>194.92</v>
+        <v>195.5</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>192.22</t>
+          <t>192.61</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>39.40</t>
         </is>
       </c>
       <c r="AQ31" t="n">
-        <v>4.54</v>
+        <v>4.9</v>
       </c>
       <c r="AR31" t="n">
-        <v>3.17</v>
+        <v>3.51</v>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
@@ -13296,7 +13320,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-68.36</t>
+          <t>-64.90</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -13306,43 +13330,43 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>28204.36402266289</t>
+          <t>28191.54526166902</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>27093.0</t>
+          <t>17273.0</t>
         </is>
       </c>
       <c r="AX31" t="n">
-        <v>25064</v>
+        <v>23978</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>22168.4</t>
+          <t>23524.2</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>12662.48</v>
+        <v>12876.32</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>453</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>1554.494789995829</t>
+          <t>1584.041988898771</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>2440.878634307883</t>
+          <t>1746.551582864951</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>27093.0</t>
+          <t>17273.0</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -13362,7 +13386,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>11.72</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -13407,7 +13431,7 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
@@ -13417,12 +13441,12 @@
       </c>
       <c r="BS31" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="BT31" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU31" t="inlineStr">
@@ -13432,7 +13456,7 @@
       </c>
       <c r="BV31" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="BW31" t="inlineStr">
@@ -13447,12 +13471,12 @@
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>9987</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -13472,7 +13496,7 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
@@ -13482,12 +13506,12 @@
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -13519,12 +13543,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13544,7 +13568,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -13554,7 +13578,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>7.97</t>
+          <t>13.06</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -13629,17 +13653,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>30.12</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -13650,12 +13674,12 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -13669,47 +13693,47 @@
         </is>
       </c>
       <c r="AH32" t="n">
-        <v>3.18</v>
+        <v>1.9</v>
       </c>
       <c r="AI32" t="n">
-        <v>3.54</v>
+        <v>4.44</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>207.4</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>200.3</v>
+        <v>201.08</v>
       </c>
       <c r="AN32" t="n">
-        <v>194.34</v>
+        <v>194.92</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>191.84</t>
+          <t>192.22</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>43.78</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="AQ32" t="n">
-        <v>4.06</v>
+        <v>4.54</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.83</v>
+        <v>3.17</v>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
@@ -13718,7 +13742,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-71.78</t>
+          <t>-68.36</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -13728,43 +13752,43 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>28204.36402266289</t>
+          <t>28191.54526166902</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>27123.0</t>
+          <t>27093.0</t>
         </is>
       </c>
       <c r="AX32" t="n">
-        <v>21655.6</v>
+        <v>25064</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>20056.7</t>
+          <t>22168.4</t>
         </is>
       </c>
       <c r="AZ32" t="n">
-        <v>12284.3</v>
+        <v>12662.48</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>1393.334091030001</t>
+          <t>1554.494789995829</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>2293.457328001074</t>
+          <t>2440.878634307883</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>27123.0</t>
+          <t>27093.0</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -13829,7 +13853,7 @@
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
@@ -13844,7 +13868,7 @@
       </c>
       <c r="BT32" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU32" t="inlineStr">
@@ -13854,7 +13878,7 @@
       </c>
       <c r="BV32" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="BW32" t="inlineStr">
@@ -13869,12 +13893,12 @@
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>9987</t>
         </is>
       </c>
       <c r="CA32" t="inlineStr">
@@ -13894,17 +13918,17 @@
       </c>
       <c r="CD32" t="inlineStr">
         <is>
+          <t>215.0</t>
+        </is>
+      </c>
+      <c r="CE32" t="inlineStr">
+        <is>
+          <t>215.5</t>
+        </is>
+      </c>
+      <c r="CF32" t="inlineStr">
+        <is>
           <t>211.0</t>
-        </is>
-      </c>
-      <c r="CE32" t="inlineStr">
-        <is>
-          <t>214.0</t>
-        </is>
-      </c>
-      <c r="CF32" t="inlineStr">
-        <is>
-          <t>210.5</t>
         </is>
       </c>
       <c r="CG32" t="inlineStr">
@@ -13941,12 +13965,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -13956,7 +13980,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -13966,7 +13990,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -13976,7 +14000,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -14036,12 +14060,12 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14051,17 +14075,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>30.12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -14072,12 +14096,12 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -14091,47 +14115,47 @@
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>2.93</v>
+        <v>3.18</v>
       </c>
       <c r="AI33" t="n">
-        <v>2.52</v>
+        <v>3.54</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>207.4</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>199.48</v>
+        <v>200.3</v>
       </c>
       <c r="AN33" t="n">
-        <v>193.8</v>
+        <v>194.34</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>191.47</t>
+          <t>191.84</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>34.99</t>
+          <t>43.78</t>
         </is>
       </c>
       <c r="AQ33" t="n">
-        <v>3.4</v>
+        <v>4.06</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.52</v>
+        <v>2.83</v>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
@@ -14140,7 +14164,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-74.87</t>
+          <t>-71.78</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -14150,43 +14174,43 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>28204.36402266289</t>
+          <t>28191.54526166902</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>22122.0</t>
+          <t>27123.0</t>
         </is>
       </c>
       <c r="AX33" t="n">
-        <v>20551.2</v>
+        <v>21655.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>18187.0</t>
+          <t>20056.7</t>
         </is>
       </c>
       <c r="AZ33" t="n">
-        <v>11819.44</v>
+        <v>12284.3</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>2364</t>
+          <t>1598</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>1229.675320671625</t>
+          <t>1393.334091030001</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>1997.731985848452</t>
+          <t>2293.457328001074</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>22122.0</t>
+          <t>27123.0</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
@@ -14206,7 +14230,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -14251,7 +14275,7 @@
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
@@ -14261,12 +14285,12 @@
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU33" t="inlineStr">
@@ -14276,7 +14300,7 @@
       </c>
       <c r="BV33" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="BW33" t="inlineStr">
@@ -14291,12 +14315,12 @@
       </c>
       <c r="BY33" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ33" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>9987</t>
         </is>
       </c>
       <c r="CA33" t="inlineStr">
@@ -14316,22 +14340,22 @@
       </c>
       <c r="CD33" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CE33" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CF33" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -14363,12 +14387,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14378,7 +14402,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -14388,7 +14412,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -14398,7 +14422,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -14458,12 +14482,12 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -14473,17 +14497,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>30.12</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -14494,12 +14518,12 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -14509,51 +14533,51 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>1.87</v>
+        <v>2.93</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.15</v>
+        <v>2.52</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>203.2</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>198.92</v>
+        <v>199.48</v>
       </c>
       <c r="AN34" t="n">
-        <v>193.33</v>
+        <v>193.8</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>191.14</t>
+          <t>191.47</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>34.99</t>
         </is>
       </c>
       <c r="AQ34" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
@@ -14562,7 +14586,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-77.07</t>
+          <t>-74.87</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -14572,43 +14596,43 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>28204.36402266289</t>
+          <t>28191.54526166902</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>26279.0</t>
+          <t>22122.0</t>
         </is>
       </c>
       <c r="AX34" t="n">
-        <v>21604.4</v>
+        <v>20551.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>18148.2</t>
+          <t>18187.0</t>
         </is>
       </c>
       <c r="AZ34" t="n">
-        <v>11512</v>
+        <v>11819.44</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>2364</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>1090.028654275838</t>
+          <t>1229.675320671625</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>2039.741068992971</t>
+          <t>1997.731985848452</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>26279.0</t>
+          <t>22122.0</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
@@ -14628,7 +14652,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -14683,12 +14707,12 @@
       </c>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU34" t="inlineStr">
@@ -14698,7 +14722,7 @@
       </c>
       <c r="BV34" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="BW34" t="inlineStr">
@@ -14713,12 +14737,12 @@
       </c>
       <c r="BY34" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ34" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>9987</t>
         </is>
       </c>
       <c r="CA34" t="inlineStr">
@@ -14738,22 +14762,22 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
+          <t>211.0</t>
+        </is>
+      </c>
+      <c r="CF34" t="inlineStr">
+        <is>
           <t>208.0</t>
         </is>
       </c>
-      <c r="CF34" t="inlineStr">
-        <is>
-          <t>202.0</t>
-        </is>
-      </c>
       <c r="CG34" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CH34" t="inlineStr">

--- a/Result/checksun_type/控制器.xlsx
+++ b/Result/checksun_type/控制器.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>498.0</t>
+          <t>358.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,149 +963,149 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>706.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-0.74</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>31.57</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-09-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-08-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>657.0</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>850.0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>525.0</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>598.0</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>-16.94</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>9.87</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025/05/15</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>261.5</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>-3.59</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>713.0</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2025/04/01</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>220.0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2026/01/07</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
           <t>731.0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-0.93</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>47.01</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-08-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>657.0</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>850.0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>525.0</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>598.0</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>-14.00</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>9.87</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025/05/15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>261.5</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>-3.04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>713.0</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>2025/04/01</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>220.0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>2026/01/07</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>731.0</t>
-        </is>
-      </c>
       <c r="AI2" t="inlineStr">
         <is>
           <t>2025/12/30</t>
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>11.18</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>358</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1159,51 +1159,51 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>47.46</t>
+          <t>20.34</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-4.39</v>
+        <v>-6.66</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.26</v>
+        <v>0.55</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>764.6</t>
+          <t>756.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>755.1</v>
+        <v>752.25</v>
       </c>
       <c r="BA2" t="n">
-        <v>720.12</v>
+        <v>719.54</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>756.29</t>
+          <t>756.62</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-37.35</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>10.78</v>
+        <v>6.26</v>
       </c>
       <c r="BE2" t="n">
-        <v>10.92</v>
+        <v>9.99</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-87.86</t>
+          <t>-88.90</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>431890.3673780487</t>
+          <t>431745.9346504559</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>372687.0</t>
+          <t>256248.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>492519.4</v>
+        <v>439301.6</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>335023.7</t>
+          <t>333890.5</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>405946.66</v>
+        <v>405540.76</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>157495</t>
+          <t>105411</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-15076.53732509762</t>
+          <t>-14161.41478042994</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>2051.744370206608</t>
+          <t>-9128.240784757712</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>372687.0</t>
+          <t>256248.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1328,17 +1328,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>18.60</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>61.84</t>
+          <t>59.73</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>49.83</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>17082</t>
+          <t>16498</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>776.0</t>
+          <t>731.0</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>781.0</t>
+          <t>734.0</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>731.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>731.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>582.0</t>
+          <t>498.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>731.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32.08</t>
+          <t>47.01</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.41</t>
+          <t>-14.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,87 +1610,87 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>358</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>80.79</t>
+          <t>47.46</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>0.5</v>
+        <v>-4.39</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.56</v>
+        <v>1.26</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>766.2</t>
+          <t>764.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>754.4</v>
+        <v>755.1</v>
       </c>
       <c r="BA3" t="n">
-        <v>720.5</v>
+        <v>720.12</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>755.61</t>
+          <t>756.29</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>26.50</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>13.86</v>
+        <v>10.78</v>
       </c>
       <c r="BE3" t="n">
-        <v>10.96</v>
+        <v>10.92</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-87.82</t>
+          <t>-87.86</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>431890.3673780487</t>
+          <t>431745.9346504559</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>459063.0</t>
+          <t>372687.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>442580</v>
+        <v>492519.4</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>335084.7</t>
+          <t>335023.7</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>404627.88</v>
+        <v>405946.66</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>107495</t>
+          <t>157495</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-18190.77036060748</t>
+          <t>-15076.53732509762</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>5474.268006933969</t>
+          <t>2051.744370206608</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>459063.0</t>
+          <t>372687.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>61.84</t>
+          <t>59.73</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>49.83</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>17082</t>
+          <t>16498</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>796.0</t>
+          <t>776.0</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>810.0</t>
+          <t>781.0</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>731.0</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>731.0</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>733.0</t>
+          <t>582.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>782.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>21.79</t>
+          <t>32.08</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.00</t>
+          <t>-9.41</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,66 +2118,66 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>358</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>81.36</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>82.49</t>
+          <t>80.79</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.34</v>
+        <v>1.56</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>762.2</t>
+          <t>766.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>752.15</v>
+        <v>754.4</v>
       </c>
       <c r="BA4" t="n">
-        <v>719.9400000000001</v>
+        <v>720.5</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>754.2</t>
+          <t>755.61</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>26.50</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>13.61</v>
+        <v>13.86</v>
       </c>
       <c r="BE4" t="n">
-        <v>10.23</v>
+        <v>10.96</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-88.63</t>
+          <t>-87.82</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>431890.3673780487</t>
+          <t>431745.9346504559</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>585311.0</t>
+          <t>459063.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>381880.4</v>
+        <v>442580</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>313558.0</t>
+          <t>335084.7</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>403486.16</v>
+        <v>404627.88</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>68322</t>
+          <t>107495</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-22493.50460925138</t>
+          <t>-18190.77036060748</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>913.5064877254772</t>
+          <t>5474.268006933969</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>585311.0</t>
+          <t>459063.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2302,17 +2302,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>20.60</t>
+          <t>20.28</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>61.84</t>
+          <t>59.73</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>49.83</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>17082</t>
+          <t>16498</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
+          <t>796.0</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
           <t>810.0</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
-        <is>
-          <t>824.0</t>
-        </is>
-      </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>782.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>675.0</t>
+          <t>733.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>793.0</t>
+          <t>782.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-8.48</t>
+          <t>-10.76</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>21.79</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-6.71</t>
+          <t>-8.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>21.09</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,66 +2605,66 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>358</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>81.36</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>73.12</t>
+          <t>82.49</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>5.23</v>
+        <v>2.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.39</v>
+        <v>1.34</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>753.6</t>
+          <t>762.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>750.7</v>
+        <v>752.15</v>
       </c>
       <c r="BA5" t="n">
-        <v>719.74</v>
+        <v>719.9400000000001</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>751.9</t>
+          <t>754.2</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>11.87</v>
+        <v>13.61</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.380000000000001</v>
+        <v>10.23</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-89.57</t>
+          <t>-88.63</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>431890.3673780487</t>
+          <t>431745.9346504559</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>523199.0</t>
+          <t>585311.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>291660.8</v>
+        <v>381880.4</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>272880.8</t>
+          <t>313558.0</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>396543.76</v>
+        <v>403486.16</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>18780</t>
+          <t>68322</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-26749.32480870172</t>
+          <t>-22493.50460925138</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-19161.06377141975</t>
+          <t>913.5064877254772</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>523199.0</t>
+          <t>585311.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2784,22 +2784,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>20.60</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>61.84</t>
+          <t>59.73</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>49.83</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>17082</t>
+          <t>16498</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>748.0</t>
+          <t>810.0</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>794.0</t>
+          <t>824.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>748.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>793.0</t>
+          <t>782.0</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>686.0</t>
+          <t>675.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>793.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-12.32</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-12.27</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-12.12</t>
+          <t>-6.71</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,87 +3071,87 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>21.09</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>358</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>66.13</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>63.44</t>
+          <t>73.12</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>0.7</v>
+        <v>5.23</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.68</v>
+        <v>0.39</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>741.8</t>
+          <t>753.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>746.9</v>
+        <v>750.7</v>
       </c>
       <c r="BA6" t="n">
         <v>719.74</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>749.54</t>
+          <t>751.9</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>8.369999999999999</v>
+        <v>11.87</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.76</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-90.26</t>
+          <t>-89.57</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>431890.3673780487</t>
+          <t>431745.9346504559</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>522337.0</t>
+          <t>523199.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>228479.4</v>
+        <v>291660.8</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>260424.7</t>
+          <t>272880.8</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>395150.9</v>
+        <v>396543.76</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-31945</t>
+          <t>18780</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-28129.00863366207</t>
+          <t>-26749.32480870172</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-40499.84043550503</t>
+          <t>-19161.06377141975</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>522337.0</t>
+          <t>523199.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3271,22 +3271,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>20.89</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>61.84</t>
+          <t>59.73</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>49.83</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>17082</t>
+          <t>16498</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>748.0</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>794.0</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>748.0</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>793.0</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>686.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,159 +3398,159 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>747.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-5.81</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-0.74</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-12.27</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-09-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-08-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>657.0</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>850.0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>525.0</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>598.0</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>-12.12</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>9.87</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025/05/15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>261.5</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>713.0</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2025/04/01</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>220.0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2026/01/07</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>731.0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/12/30</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
           <t>739.0</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-1.09</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-0.93</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-28.24</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-08-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>657.0</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>850.0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>525.0</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>598.0</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>-13.06</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>9.87</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025/05/15</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>261.5</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>-0.7</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>713.0</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2025/04/01</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>220.0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>2026/01/07</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>731.0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>2025/12/30</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>739.0</t>
-        </is>
-      </c>
       <c r="AK7" t="inlineStr">
         <is>
           <t>2026-01-06 00:00:00</t>
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,66 +3579,66 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>358</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>53.23</t>
+          <t>66.13</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>63.44</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.46</v>
+        <v>0.7</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.03</v>
+        <v>-0.68</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>742.4</t>
+          <t>741.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>742.15</v>
+        <v>746.9</v>
       </c>
       <c r="BA7" t="n">
-        <v>720.64</v>
+        <v>719.74</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>747.58</t>
+          <t>749.54</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>8.449999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.859999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-90.15</t>
+          <t>-90.26</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>431890.3673780487</t>
+          <t>431745.9346504559</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>122990.0</t>
+          <t>522337.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>177528</v>
+        <v>228479.4</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>247402.9</t>
+          <t>260424.7</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>395832</v>
+        <v>395150.9</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-69874</t>
+          <t>-31945</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-25879.76648787244</t>
+          <t>-28129.00863366207</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-69445.02708293026</t>
+          <t>-40499.84043550503</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>122990.0</t>
+          <t>522337.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3758,22 +3758,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>19.47</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>61.84</t>
+          <t>59.73</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>49.83</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>17082</t>
+          <t>16498</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>763.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>743.0</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>747.0</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3860,7 +3860,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-17.81</t>
+          <t>-28.24</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-11.76</t>
+          <t>-13.06</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,66 +4066,66 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>358</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>70.97</t>
+          <t>53.23</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>52.25</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>0.24</v>
+        <v>-0.46</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.44</v>
+        <v>0.03</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>748.2</t>
+          <t>742.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>737.55</v>
+        <v>742.15</v>
       </c>
       <c r="BA8" t="n">
-        <v>722.04</v>
+        <v>720.64</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>745.74</t>
+          <t>747.58</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>9.25</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.960000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-90.04</t>
+          <t>-90.15</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>431890.3673780487</t>
+          <t>431745.9346504559</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>155565.0</t>
+          <t>122990.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>227589.4</v>
+        <v>177528</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>276892.5</t>
+          <t>247402.9</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>405535.36</v>
+        <v>395832</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-49303</t>
+          <t>-69874</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-17958.81001604375</t>
+          <t>-25879.76648787244</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-65527.93561200448</t>
+          <t>-69445.02708293026</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>155565.0</t>
+          <t>122990.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>19.76</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>61.84</t>
+          <t>59.73</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>49.83</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>17082</t>
+          <t>16498</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>757.0</t>
+          <t>763.0</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,159 +4372,159 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>750.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-6.23</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-0.74</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-17.81</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-09-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-08-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>657.0</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>850.0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>525.0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>598.0</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>-11.76</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>9.87</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025/05/15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>261.5</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>713.0</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>2025/04/01</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>220.0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2026/01/07</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>731.0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/12/30</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
           <t>739.0</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-1.09</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-0.93</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-26.26</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-08-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>657.0</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>850.0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>525.0</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>598.0</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>-13.06</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>9.87</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025/05/15</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>261.5</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>-0.72</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>713.0</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>2025/04/01</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>220.0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>2026/01/07</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>731.0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>2025/12/30</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>739.0</t>
-        </is>
-      </c>
       <c r="AK9" t="inlineStr">
         <is>
           <t>2026-01-06 00:00:00</t>
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,66 +4553,66 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>358</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>53.23</t>
+          <t>70.97</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>42.56</t>
+          <t>52.25</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.59</v>
+        <v>0.24</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>743.4</t>
+          <t>748.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>732.8</v>
+        <v>737.55</v>
       </c>
       <c r="BA9" t="n">
-        <v>723.74</v>
+        <v>722.04</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>743.74</t>
+          <t>745.74</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>9.01</v>
+        <v>9.25</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.890000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-90.11</t>
+          <t>-90.04</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>431890.3673780487</t>
+          <t>431745.9346504559</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>134213.0</t>
+          <t>155565.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>245235.6</v>
+        <v>227589.4</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>332585.9</t>
+          <t>276892.5</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>411656.92</v>
+        <v>405535.36</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-87350</t>
+          <t>-49303</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-9309.87808950543</t>
+          <t>-17958.81001604375</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-61081.98581025319</t>
+          <t>-65527.93561200448</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>134213.0</t>
+          <t>155565.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>19.47</t>
+          <t>19.76</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>61.84</t>
+          <t>59.73</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>49.83</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>17082</t>
+          <t>16498</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>734.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>757.0</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>731.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>278.0</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>734.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-41.08</t>
+          <t>-26.26</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-13.65</t>
+          <t>-13.06</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,87 +5019,87 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>358</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>32.56</t>
+          <t>53.23</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>42.56</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.38</v>
+        <v>-0.59</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>736.8</t>
+          <t>743.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>727.75</v>
+        <v>732.8</v>
       </c>
       <c r="BA10" t="n">
-        <v>725.5599999999999</v>
+        <v>723.74</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>742.11</t>
+          <t>743.74</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>9.699999999999999</v>
+        <v>9.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.859999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-90.15</t>
+          <t>-90.11</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>431890.3673780487</t>
+          <t>431745.9346504559</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>207292.0</t>
+          <t>134213.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>254100.8</v>
+        <v>245235.6</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>431287.4</t>
+          <t>332585.9</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>425176.36</v>
+        <v>411656.92</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-177186</t>
+          <t>-87350</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>103.2324051759833</t>
+          <t>-9309.87808950543</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-50261.41517167084</t>
+          <t>-61081.98581025319</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>207292.0</t>
+          <t>134213.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>61.84</t>
+          <t>59.73</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>49.83</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>17082</t>
+          <t>16498</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>751.0</t>
+          <t>734.0</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>764.0</t>
+          <t>747.0</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>734.0</t>
+          <t>731.0</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>734.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5321,7 +5321,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>價_量;【b1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-4.2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1194.0</t>
+          <t>490.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>97.66</t>
+          <t>79.32</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>30.91</t>
+          <t>12.68</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,66 +5527,66 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>490</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>81.56</t>
+          <t>68.16</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>93.85</t>
+          <t>83.24</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>4.62</v>
+        <v>-2.51</v>
       </c>
       <c r="AV11" t="n">
-        <v>20.22</v>
+        <v>21.78</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>27.48</t>
+          <t>28.26</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>22.86</v>
+        <v>23.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>21.36</v>
+        <v>21.47</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.79</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>88.39</t>
+          <t>63.09</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-64.36</t>
+          <t>-57.68</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,48 +5605,48 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>33149.54200819672</t>
+          <t>33123.66564417178</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>34810.0</t>
+          <t>13664.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>40673</v>
+        <v>39200</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>20577.3</t>
+          <t>21860.6</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>4709.44</v>
+        <v>4972.52</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>20095</t>
+          <t>17339</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>3363.613050153122</t>
+          <t>3914.027616029304</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>9439.990407147452</t>
+          <t>6941.307728348307</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>34810.0</t>
+          <t>13664.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5706,17 +5706,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>804</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>27.45</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3863.0</t>
+          <t>1194.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.04</t>
+          <t>97.66</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>30.91</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,66 +6014,66 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>490</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>81.56</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.85</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>16.79</v>
+        <v>4.62</v>
       </c>
       <c r="AV12" t="n">
-        <v>16.04</v>
+        <v>20.22</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>27.48</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>22.43</v>
+        <v>22.86</v>
       </c>
       <c r="BA12" t="n">
-        <v>21.23</v>
+        <v>21.36</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>114.23</t>
+          <t>88.39</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>1.69</v>
+        <v>1.91</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.79</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-72.23</t>
+          <t>-64.36</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,48 +6092,48 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>33149.54200819672</t>
+          <t>33123.66564417178</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>118552.0</t>
+          <t>34810.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>33771.2</v>
+        <v>40673</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>17226.4</t>
+          <t>20577.3</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>4025.68</v>
+        <v>4709.44</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>16544</t>
+          <t>20095</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>2258.817167063244</t>
+          <t>3363.613050153122</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>10406.75171946239</t>
+          <t>9439.990407147452</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>118552.0</t>
+          <t>34810.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>32.18</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>804</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>599.0</t>
+          <t>3863.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-10.34</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>88.44</t>
+          <t>96.04</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>16.92</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>15.51</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,12 +6501,12 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>490</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -6520,47 +6520,47 @@
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>17.99</v>
+        <v>16.79</v>
       </c>
       <c r="AV13" t="n">
-        <v>10.56</v>
+        <v>16.04</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>21.92</v>
+        <v>22.43</v>
       </c>
       <c r="BA13" t="n">
-        <v>21.06</v>
+        <v>21.23</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>116.35</t>
+          <t>114.23</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>1.22</v>
+        <v>1.69</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-80.16</t>
+          <t>-72.23</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,48 +6579,48 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>33149.54200819672</t>
+          <t>33123.66564417178</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>17130.0</t>
+          <t>118552.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>10194.2</v>
+        <v>33771.2</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>5409.7</t>
+          <t>17226.4</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>1665.38</v>
+        <v>4025.68</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>16544</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>777.37452117249</t>
+          <t>2258.817167063244</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>2443.812461360072</t>
+          <t>10406.75171946239</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>17130.0</t>
+          <t>118552.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>39.77</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6680,17 +6680,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>804</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>456.0</t>
+          <t>599.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,74 +6807,74 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>28.6</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-3.81</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>88.44</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-01-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-01-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>26.0</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>9.57</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>82.16</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2026-01-02</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2026-01-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2026-01-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>26.0</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
       <c r="T14" t="inlineStr">
         <is>
           <t>22.25</t>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>15.51</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -6988,12 +6988,12 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>490</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -7003,51 +7003,51 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>74.07</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>13.69</v>
+        <v>17.99</v>
       </c>
       <c r="AV14" t="n">
-        <v>6.25</v>
+        <v>10.56</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>21.52</v>
+        <v>21.92</v>
       </c>
       <c r="BA14" t="n">
-        <v>20.94</v>
+        <v>21.06</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>21.56</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>96.24</t>
+          <t>116.35</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>0.78</v>
+        <v>1.22</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-85.93</t>
+          <t>-80.16</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,48 +7066,48 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>33149.54200819672</t>
+          <t>33123.66564417178</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>11844.0</t>
+          <t>17130.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>6833</v>
+        <v>10194.2</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>3751.1</t>
+          <t>5409.7</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>1341.62</v>
+        <v>1665.38</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>4784</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>474.3858047747478</t>
+          <t>777.37452117249</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>1847.548790451045</t>
+          <t>2443.812461360072</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>11844.0</t>
+          <t>17130.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>804</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>894.0</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,149 +7294,149 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>5.63</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>82.16</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-01-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-01-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>22.25</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>21.85</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>18.99</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025/08/01</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>23.65</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>17.74</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>69.93</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2026-01-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2026-01-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>22.25</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2025/09/26</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>22.3</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>2025/07/04</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>17.9</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
         <is>
           <t>21.85</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>18.99</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025/08/01</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>23.65</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>0.11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2025/09/26</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>22.3</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>2025/07/04</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>17.9</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>21.85</t>
-        </is>
-      </c>
       <c r="AI15" t="inlineStr">
         <is>
           <t>2025/10/08</t>
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>23.14</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,12 +7475,12 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>490</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -7490,51 +7490,51 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>49.07</t>
+          <t>74.07</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>7.21</v>
+        <v>13.69</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.86</v>
+        <v>6.25</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>22.06</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>21.24</v>
+        <v>21.52</v>
       </c>
       <c r="BA15" t="n">
-        <v>20.87</v>
+        <v>20.94</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>96.24</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>0.48</v>
+        <v>0.78</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-89.32</t>
+          <t>-85.93</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,48 +7553,48 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>33149.54200819672</t>
+          <t>33123.66564417178</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>21029.0</t>
+          <t>11844.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>4521.2</v>
+        <v>6833</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>2660.7</t>
+          <t>3751.1</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>1132.54</v>
+        <v>1341.62</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>224.7198073790574</t>
+          <t>474.3858047747478</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>1496.116803779184</t>
+          <t>1847.548790451045</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>21029.0</t>
+          <t>11844.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>8.74</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>804</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>894.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-29.88</t>
+          <t>69.93</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>23.14</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>490</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>38.36</t>
+          <t>49.07</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-1.24</v>
+        <v>7.21</v>
       </c>
       <c r="AV16" t="n">
-        <v>3.32</v>
+        <v>3.86</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>21.77</t>
+          <t>22.06</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>21.07</v>
+        <v>21.24</v>
       </c>
       <c r="BA16" t="n">
-        <v>20.85</v>
+        <v>20.87</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>21.41</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>0.33</v>
+        <v>0.48</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-90.89</t>
+          <t>-89.32</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>33149.54200819672</t>
+          <t>33123.66564417178</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>301.0</t>
+          <t>21029.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>481.6</v>
+        <v>4521.2</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>686.8</t>
+          <t>2660.7</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>913.1</v>
+        <v>1132.54</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-205</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-6.443282875511107</t>
+          <t>224.7198073790574</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-43.46877731558754</t>
+          <t>1496.116803779184</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>301.0</t>
+          <t>21029.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>8.74</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,17 +8141,17 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>804</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-7.98</t>
+          <t>-29.88</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>490</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>38.36</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-1.83</v>
+        <v>-1.24</v>
       </c>
       <c r="AV17" t="n">
-        <v>4</v>
+        <v>3.32</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>21.77</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>21.01</v>
+        <v>21.07</v>
       </c>
       <c r="BA17" t="n">
-        <v>20.88</v>
+        <v>20.85</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>21.42</t>
+          <t>21.41</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>44.81</t>
+          <t>27.43</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-91.52</t>
+          <t>-90.89</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>33149.54200819672</t>
+          <t>33123.66564417178</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>667.0</t>
+          <t>301.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>681.6</v>
+        <v>481.6</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>740.7</t>
+          <t>686.8</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>1031.88</v>
+        <v>913.1</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-59</t>
+          <t>-205</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>0.2886252045027908</t>
+          <t>-6.443282875511107</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-20.46715111827655</t>
+          <t>-43.46877731558754</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>667.0</t>
+          <t>301.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>804</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>22.14</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-22.49</t>
+          <t>-7.98</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,66 +8936,66 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>490</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>67.86</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>-0.37</v>
+        <v>-1.83</v>
       </c>
       <c r="AV18" t="n">
-        <v>4.29</v>
+        <v>4</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>21.83</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>20.93</v>
+        <v>21.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>20.87</v>
+        <v>20.88</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>21.42</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>74.59</t>
+          <t>44.81</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-92.47</t>
+          <t>-91.52</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>33149.54200819672</t>
+          <t>33123.66564417178</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>324.0</t>
+          <t>667.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>625.2</v>
+        <v>681.6</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>806.6</t>
+          <t>740.7</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>1038.68</v>
+        <v>1031.88</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-181</t>
+          <t>-59</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>4.062402717735398</t>
+          <t>0.2886252045027908</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-26.0910011536082</t>
+          <t>-20.46715111827655</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>324.0</t>
+          <t>667.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>804</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,12 +9180,12 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9217,7 +9217,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,139 +9252,139 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
+          <t>21.05</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-22.49</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-01-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2026-01-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>22.25</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>21.85</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>18.99</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025/08/01</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>23.65</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>-20.52</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2026-01-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2026-01-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>22.25</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2025/09/26</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>22.3</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>2025/07/04</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>17.9</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
         <is>
           <t>21.85</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>18.99</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2025/08/01</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>23.65</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>2025/09/26</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>22.3</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>2025/07/04</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>17.9</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>21.85</t>
-        </is>
-      </c>
       <c r="AI19" t="inlineStr">
         <is>
           <t>2025/10/08</t>
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,66 +9423,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>490</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>82.14</t>
+          <t>67.86</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>94.05</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>0.97</v>
+        <v>-0.37</v>
       </c>
       <c r="AV19" t="n">
-        <v>4.36</v>
+        <v>4.29</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>21.83</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>20.83</v>
+        <v>20.93</v>
       </c>
       <c r="BA19" t="n">
-        <v>20.86</v>
+        <v>20.87</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.44</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>111.99</t>
+          <t>74.59</t>
         </is>
       </c>
       <c r="BD19" t="n">
         <v>0.37</v>
       </c>
       <c r="BE19" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-93.87</t>
+          <t>-92.47</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>33149.54200819672</t>
+          <t>33123.66564417178</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>285.0</t>
+          <t>324.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>669.2</v>
+        <v>625.2</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>842.0</t>
+          <t>806.6</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>1039.36</v>
+        <v>1038.68</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-172</t>
+          <t>-181</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>9.544839785252417</t>
+          <t>4.062402717735398</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>3.556748837118334</t>
+          <t>-26.0910011536082</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>285.0</t>
+          <t>324.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>804</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>19.87</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,66 +9910,66 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>11.36</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.45</v>
       </c>
       <c r="AV20" t="n">
         <v>-1.68</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>201.4</t>
+          <t>200.9</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>204.85</v>
+        <v>204.32</v>
       </c>
       <c r="BA20" t="n">
-        <v>204.25</v>
+        <v>204.3</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>198.91</t>
+          <t>199.08</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-201.35</t>
+          <t>-129.76</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>-1.22</v>
+        <v>-1.38</v>
       </c>
       <c r="BE20" t="n">
-        <v>-0.41</v>
+        <v>-0.6</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-109.04</t>
+          <t>-113.38</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>21143.37295081967</t>
+          <t>21111.3527607362</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>8313.0</t>
+          <t>3657.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>10993.2</v>
+        <v>9460.6</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>8262.7</t>
+          <t>7892.2</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>12073.36</v>
+        <v>11855.04</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>2730</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-565.3973969807547</t>
+          <t>-514.5051017130997</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>193.249279542837</t>
+          <t>-234.5974777409974</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>8313.0</t>
+          <t>3657.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
@@ -10104,7 +10104,7 @@
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>9511</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10149,19 +10149,19 @@
       </c>
       <c r="CP20" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
+          <t>199.5</t>
+        </is>
+      </c>
+      <c r="CR20" t="inlineStr">
+        <is>
           <t>200.5</t>
         </is>
       </c>
-      <c r="CR20" t="inlineStr">
-        <is>
-          <t>201.5</t>
-        </is>
-      </c>
       <c r="CS20" t="inlineStr">
         <is>
           <t>199.5</t>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>27.61</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,17 +10397,17 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
@@ -10416,47 +10416,47 @@
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-0.2</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AV21" t="n">
-        <v>-1.45</v>
+        <v>-1.68</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>202.4</t>
+          <t>201.4</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>205.38</v>
+        <v>204.85</v>
       </c>
       <c r="BA21" t="n">
         <v>204.25</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>198.76</t>
+          <t>198.91</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-373.17</t>
+          <t>-201.35</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-0.95</v>
+        <v>-1.22</v>
       </c>
       <c r="BE21" t="n">
-        <v>-0.2</v>
+        <v>-0.41</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-104.49</t>
+          <t>-109.04</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>21143.37295081967</t>
+          <t>21111.3527607362</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>7192.0</t>
+          <t>8313.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>10046.2</v>
+        <v>10993.2</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>7872.7</t>
+          <t>8262.7</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>12159.28</v>
+        <v>12073.36</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>2173</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-703.3331563486804</t>
+          <t>-565.3973969807547</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>298.7000299646406</t>
+          <t>193.249279542837</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>7192.0</t>
+          <t>8313.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>9511</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10636,7 +10636,7 @@
       </c>
       <c r="CP21" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CQ21" t="inlineStr">
@@ -10646,17 +10646,17 @@
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,7 +10713,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>27.61</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10863,17 +10863,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,66 +10884,66 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>-1.09</v>
+        <v>-0.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>-1.46</v>
+        <v>-1.45</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>202.7</t>
+          <t>202.4</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>205.7</v>
+        <v>205.38</v>
       </c>
       <c r="BA22" t="n">
-        <v>204.21</v>
+        <v>204.25</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>198.57</t>
+          <t>198.76</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-6189.52</t>
+          <t>-373.17</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>-0.85</v>
+        <v>-0.95</v>
       </c>
       <c r="BE22" t="n">
-        <v>-0.01</v>
+        <v>-0.2</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-100.30</t>
+          <t>-104.49</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>21143.37295081967</t>
+          <t>21111.3527607362</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>20693.0</t>
+          <t>7192.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>10275.8</v>
+        <v>10046.2</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>7465.0</t>
+          <t>7872.7</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>12365.58</v>
+        <v>12159.28</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>2173</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>-885.521008405648</t>
+          <t>-703.3331563486804</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>558.7832437827656</t>
+          <t>298.7000299646406</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>20693.0</t>
+          <t>7192.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11068,17 +11068,17 @@
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>9511</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11123,27 +11123,27 @@
       </c>
       <c r="CP22" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,42 +11175,42 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>-0.98</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>200.5</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>37.0</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>202.5</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>8.71</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,12 +11371,12 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -11386,51 +11386,51 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>-0.54</v>
+        <v>-1.09</v>
       </c>
       <c r="AV23" t="n">
-        <v>-1.27</v>
+        <v>-1.46</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>203.6</t>
+          <t>202.7</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>206.22</v>
+        <v>205.7</v>
       </c>
       <c r="BA23" t="n">
-        <v>204.16</v>
+        <v>204.21</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>198.4</t>
+          <t>198.57</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-382.87</t>
+          <t>-6189.52</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>-0.55</v>
+        <v>-0.85</v>
       </c>
       <c r="BE23" t="n">
-        <v>0.2</v>
+        <v>-0.01</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-95.64</t>
+          <t>-100.30</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>21143.37295081967</t>
+          <t>21111.3527607362</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>7448.0</t>
+          <t>20693.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>7072.6</v>
+        <v>10275.8</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>5602.2</t>
+          <t>7465.0</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>12238.84</v>
+        <v>12365.58</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-1148.121781530814</t>
+          <t>-885.521008405648</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>-536.1615666121561</t>
+          <t>558.7832437827656</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>7448.0</t>
+          <t>20693.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11550,22 +11550,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>9511</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11610,27 +11610,27 @@
       </c>
       <c r="CP23" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>202.5</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>202.5</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>202.5</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>18.10</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11837,12 +11837,12 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>8.71</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
@@ -11858,12 +11858,12 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -11873,51 +11873,51 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>-0.93</v>
+        <v>-0.54</v>
       </c>
       <c r="AV24" t="n">
-        <v>-1.09</v>
+        <v>-1.27</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>204.4</t>
+          <t>203.6</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>206.65</v>
+        <v>206.22</v>
       </c>
       <c r="BA24" t="n">
-        <v>204.02</v>
+        <v>204.16</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>198.19</t>
+          <t>198.4</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-196.62</t>
+          <t>-382.87</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>-0.37</v>
+        <v>-0.55</v>
       </c>
       <c r="BE24" t="n">
-        <v>0.38</v>
+        <v>0.2</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-91.47</t>
+          <t>-95.64</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>21143.37295081967</t>
+          <t>21111.3527607362</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>11320.0</t>
+          <t>7448.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>6323.8</v>
+        <v>7072.6</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>5354.5</t>
+          <t>5602.2</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>12396.84</v>
+        <v>12238.84</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>-1259.387275152388</t>
+          <t>-1148.121781530814</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>-662.1126683687517</t>
+          <t>-536.1615666121561</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>11320.0</t>
+          <t>7448.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -12037,12 +12037,12 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>9511</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12097,22 +12097,22 @@
       </c>
       <c r="CP24" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>202.5</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>202.5</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>202.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>18.10</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12324,17 +12324,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,66 +12345,66 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>-0.24</v>
+        <v>-0.93</v>
       </c>
       <c r="AV25" t="n">
-        <v>-1.07</v>
+        <v>-1.09</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>204.4</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>207.22</v>
+        <v>206.65</v>
       </c>
       <c r="BA25" t="n">
-        <v>203.85</v>
+        <v>204.02</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>197.99</t>
+          <t>198.19</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-122.84</t>
+          <t>-196.62</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>-0.13</v>
+        <v>-0.37</v>
       </c>
       <c r="BE25" t="n">
-        <v>0.57</v>
+        <v>0.38</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-87.28</t>
+          <t>-91.47</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>21143.37295081967</t>
+          <t>21111.3527607362</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>3578.0</t>
+          <t>11320.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>5532.2</v>
+        <v>6323.8</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>4911.1</t>
+          <t>5354.5</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>12363.24</v>
+        <v>12396.84</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>969</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>-1367.982658203959</t>
+          <t>-1259.387275152388</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>-1233.25307557929</t>
+          <t>-662.1126683687517</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>3578.0</t>
+          <t>11320.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12529,17 +12529,17 @@
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>9511</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="CP25" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CQ25" t="inlineStr">
@@ -12594,17 +12594,17 @@
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>202.5</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,7 +12661,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>12.65</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,66 +12832,66 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AU26" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="AV26" t="n">
         <v>-1.07</v>
       </c>
-      <c r="AV26" t="n">
-        <v>-0.95</v>
-      </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>205.7</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>207.68</v>
+        <v>207.22</v>
       </c>
       <c r="BA26" t="n">
-        <v>203.62</v>
+        <v>203.85</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>197.76</t>
+          <t>197.99</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-103.51</t>
+          <t>-122.84</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>-0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="BE26" t="n">
-        <v>0.75</v>
+        <v>0.57</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-83.37</t>
+          <t>-87.28</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>21143.37295081967</t>
+          <t>21111.3527607362</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>8340.0</t>
+          <t>3578.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>5699.2</v>
+        <v>5532.2</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>5516.4</t>
+          <t>4911.1</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>12436.32</v>
+        <v>12363.24</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>621</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>-1392.478945953899</t>
+          <t>-1367.982658203959</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>-1175.623190323655</t>
+          <t>-1233.25307557929</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>8340.0</t>
+          <t>3578.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>9511</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13071,19 +13071,19 @@
       </c>
       <c r="CP26" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
+          <t>203.5</t>
+        </is>
+      </c>
+      <c r="CR26" t="inlineStr">
+        <is>
           <t>205.0</t>
         </is>
       </c>
-      <c r="CR26" t="inlineStr">
-        <is>
-          <t>205.0</t>
-        </is>
-      </c>
       <c r="CS26" t="inlineStr">
         <is>
           <t>203.5</t>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>203.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-11.43</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13298,17 +13298,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,66 +13319,66 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr">
+        <is>
           <t>40.0</t>
         </is>
       </c>
-      <c r="AT27" t="inlineStr">
-        <is>
-          <t>53.33</t>
-        </is>
-      </c>
       <c r="AU27" t="n">
-        <v>-0.39</v>
+        <v>-1.07</v>
       </c>
       <c r="AV27" t="n">
-        <v>-1.19</v>
+        <v>-0.95</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>205.8</t>
+          <t>205.7</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>208.28</v>
+        <v>207.68</v>
       </c>
       <c r="BA27" t="n">
-        <v>203.43</v>
+        <v>203.62</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>197.54</t>
+          <t>197.76</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-77.77</t>
+          <t>-103.51</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>0.21</v>
+        <v>-0.03</v>
       </c>
       <c r="BE27" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-79.07</t>
+          <t>-83.37</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>21143.37295081967</t>
+          <t>21111.3527607362</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>4677.0</t>
+          <t>8340.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>4654.2</v>
+        <v>5699.2</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>5255.0</t>
+          <t>5516.4</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>12528.8</v>
+        <v>12436.32</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>-600</t>
+          <t>182</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>-1431.907265159397</t>
+          <t>-1392.478945953899</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>-1561.522526018332</t>
+          <t>-1175.623190323655</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>4677.0</t>
+          <t>8340.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>9511</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13558,27 +13558,27 @@
       </c>
       <c r="CP27" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>203.5</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>203.5</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,7 +13635,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -13645,7 +13645,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-44.83</t>
+          <t>-11.43</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13655,7 +13655,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13785,17 +13785,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,33 +13806,33 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>59.61</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>0.54</v>
+        <v>-0.39</v>
       </c>
       <c r="AV28" t="n">
-        <v>-1.6</v>
+        <v>-1.19</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -13842,30 +13842,30 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>205.4</t>
+          <t>205.8</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>208.75</v>
+        <v>208.28</v>
       </c>
       <c r="BA28" t="n">
-        <v>203.21</v>
+        <v>203.43</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>197.33</t>
+          <t>197.54</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-68.51</t>
+          <t>-77.77</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>0.35</v>
+        <v>0.21</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.12</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-75.00</t>
+          <t>-79.07</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>21143.37295081967</t>
+          <t>21111.3527607362</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>3704.0</t>
+          <t>4677.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>4131.8</v>
+        <v>4654.2</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>7489.2</t>
+          <t>5255.0</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>12694.38</v>
+        <v>12528.8</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>-3357</t>
+          <t>-600</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>-1408.340854094136</t>
+          <t>-1431.907265159397</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>-1664.574343938646</t>
+          <t>-1561.522526018332</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>3704.0</t>
+          <t>4677.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -13995,12 +13995,12 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>9511</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14045,27 +14045,27 @@
       </c>
       <c r="CP28" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>207.5</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">
